--- a/output/pdf_financials_xlsx/PCRX.xlsx
+++ b/output/pdf_financials_xlsx/PCRX.xlsx
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000715</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.046092</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.107532</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.381248</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.293958</v>
       </c>
     </row>
     <row r="13">
@@ -1033,19 +1033,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.025818</v>
+        <v>-0.026533</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.517085</v>
+        <v>-0.563177</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.517085</v>
+        <v>-0.624617</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.157386</v>
+        <v>-1.538634</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.8358</v>
+        <v>-1.129758</v>
       </c>
     </row>
     <row r="28">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.025818</v>
+        <v>-0.026533</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.517085</v>
+        <v>-0.563177</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.517085</v>
+        <v>-0.624617</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.8675119999999999</v>
+        <v>-1.24876</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.104396</v>
+        <v>-0.189562</v>
       </c>
     </row>
     <row r="30">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-14.97023079203591</v>
+        <v>-21.54924128295951</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.4996337075576849</v>
+        <v>-0.9072336571520926</v>
       </c>
     </row>
     <row r="31">
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>12.886556</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>25.885295</v>
       </c>
     </row>
     <row r="35">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>12.886556</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>25.885295</v>
       </c>
     </row>
     <row r="37">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.934582</v>
+        <v>0.048026</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>25.966149</v>
+        <v>0.080854</v>
       </c>
     </row>
     <row r="49">
@@ -3698,10 +3698,10 @@
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.05825</v>
+        <v>-0.107077</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>-0.184935</v>
+        <v>-0.322987</v>
       </c>
     </row>
     <row r="125">
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-0.05825</v>
+        <v>-0.107077</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>-0.184935</v>
+        <v>-0.322987</v>
       </c>
     </row>
     <row r="126">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5913,7 +5913,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -7530,7 +7534,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7944,7 +7948,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8643,7 +8647,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">

--- a/output/pdf_financials_xlsx/PCRX.xlsx
+++ b/output/pdf_financials_xlsx/PCRX.xlsx
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>0.283154</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.405663</v>
       </c>
     </row>
     <row r="108">
@@ -4873,7 +4873,11 @@
           <t>Lease liabilities 8</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -5347,7 +5351,11 @@
           <t>Deferred tax recovery 13</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -5468,7 +5476,11 @@
           <t>Share-based payment expense 11</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5792,7 +5804,11 @@
           <t>Net proceeds from share issuance 11</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -6708,7 +6724,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>1</v>
       </c>
